--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\arrowNew\AAAGameData\DataTables\Core\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\Core\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="16575"/>
+    <workbookView windowWidth="27000" windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -124,6 +124,30 @@
     <t>ArrowUITopbar</t>
   </si>
   <si>
+    <t>大厅tab</t>
+  </si>
+  <si>
+    <t>HallTabUIForm</t>
+  </si>
+  <si>
+    <t>大厅主界面</t>
+  </si>
+  <si>
+    <t>HomePageUIForm</t>
+  </si>
+  <si>
+    <t>设置界面</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm</t>
+  </si>
+  <si>
+    <t>任务界面</t>
+  </si>
+  <si>
+    <t>TaskPageUIForm</t>
+  </si>
+  <si>
     <t>对话框(中层)</t>
   </si>
   <si>
@@ -154,24 +178,6 @@
     <t>ArrowRewardDialogUIForm</t>
   </si>
   <si>
-    <t>提现</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm</t>
-  </si>
-  <si>
-    <t>支付方式</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm</t>
-  </si>
-  <si>
-    <t>确认提现方式</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm</t>
-  </si>
-  <si>
     <t>PrivacyPolicy隐私协议</t>
   </si>
   <si>
@@ -182,42 +188,6 @@
   </si>
   <si>
     <t>ArrowGuideUIForm</t>
-  </si>
-  <si>
-    <t>提现记录</t>
-  </si>
-  <si>
-    <t>ArrowMakeupOrdemUIForm</t>
-  </si>
-  <si>
-    <t>提现说明</t>
-  </si>
-  <si>
-    <t>ArrowMakeupTipsUIForm</t>
-  </si>
-  <si>
-    <t>提现引导</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm</t>
-  </si>
-  <si>
-    <t>扭蛋奖励界面</t>
-  </si>
-  <si>
-    <t>ArrowCapsuleToysUIForm</t>
-  </si>
-  <si>
-    <t>刮卡界面</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardUIForm</t>
-  </si>
-  <si>
-    <t>刮卡奖励界面</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm</t>
   </si>
   <si>
     <t>奖励领取界面</t>
@@ -1188,7 +1158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1378,171 +1348,175 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
+      <c r="A11" s="1"/>
       <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
+      <c r="A12" s="1"/>
       <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1"/>
+      <c r="A13" s="1"/>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:8">
       <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="B18">
         <v>11</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
@@ -1551,13 +1525,13 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="1:8">
       <c r="B19">
         <v>12</v>
       </c>
@@ -1565,7 +1539,7 @@
         <v>39</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>40</v>
@@ -1580,7 +1554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="1:8">
       <c r="B20">
         <v>13</v>
       </c>
@@ -1588,7 +1562,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
         <v>42</v>
@@ -1597,13 +1571,13 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="1:8">
       <c r="B21">
         <v>14</v>
       </c>
@@ -1611,7 +1585,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>44</v>
@@ -1620,13 +1594,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="1:8">
       <c r="B22">
         <v>15</v>
       </c>
@@ -1643,124 +1617,9 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23">
-        <v>11</v>
-      </c>
-      <c r="E23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25">
-        <v>18</v>
-      </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26">
-        <v>19</v>
-      </c>
-      <c r="C26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26">
-        <v>13</v>
-      </c>
-      <c r="E26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27">
-        <v>20</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27">
-        <v>13</v>
-      </c>
-      <c r="E27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>#</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>ArrowRewardUIForm</t>
+  </si>
+  <si>
+    <t>提现界面</t>
+  </si>
+  <si>
+    <t>MakeupUIForm</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1620,6 +1626,29 @@
         <v>2</v>
       </c>
       <c r="H22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -200,6 +200,18 @@
   </si>
   <si>
     <t>MakeupUIForm</t>
+  </si>
+  <si>
+    <t>提现方式界面</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm</t>
+  </si>
+  <si>
+    <t>提现信息界面</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1649,6 +1661,52 @@
         <v>2</v>
       </c>
       <c r="H23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="B24">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="B25">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>MakeupInfoUIForm</t>
+  </si>
+  <si>
+    <t>提现记录界面</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1182,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1707,6 +1713,29 @@
         <v>2</v>
       </c>
       <c r="H25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="B26">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="17175"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>MakeupRecordUIForm</t>
+  </si>
+  <si>
+    <t>玩法界面</t>
+  </si>
+  <si>
+    <t>PlayUIForm</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1736,6 +1742,29 @@
         <v>2</v>
       </c>
       <c r="H26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -224,6 +224,21 @@
   </si>
   <si>
     <t>PlayUIForm</t>
+  </si>
+  <si>
+    <t>p卡领取界面</t>
+  </si>
+  <si>
+    <t>PcardRewardUIForm</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm</t>
+  </si>
+  <si>
+    <t>测试界面</t>
+  </si>
+  <si>
+    <t>DebugUIForm</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1203,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1765,6 +1780,75 @@
         <v>2</v>
       </c>
       <c r="H27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="B28">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="B29">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+      <c r="H30" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>DebugUIForm</t>
+  </si>
+  <si>
+    <t>通关界面</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1849,6 +1855,29 @@
         <v>2</v>
       </c>
       <c r="H30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
   <si>
     <t>#</t>
   </si>
@@ -146,6 +146,12 @@
   </si>
   <si>
     <t>TaskPageUIForm</t>
+  </si>
+  <si>
+    <t>退出确认界面</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm</t>
   </si>
   <si>
     <t>对话框(中层)</t>
@@ -1209,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1495,37 +1501,38 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="B15">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
+      <c r="C15" s="1"/>
+      <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:8">
       <c r="B16">
@@ -1535,13 +1542,13 @@
         <v>34</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1551,46 +1558,46 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="B18">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>4</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
+      <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:8">
       <c r="B19">
         <v>12</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>40</v>
@@ -1599,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -1613,7 +1620,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>42</v>
@@ -1636,7 +1643,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
         <v>44</v>
@@ -1645,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -1659,7 +1666,7 @@
         <v>45</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E22" t="s">
         <v>46</v>
@@ -1668,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -1682,7 +1689,7 @@
         <v>47</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
         <v>48</v>
@@ -1705,7 +1712,7 @@
         <v>49</v>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
@@ -1751,7 +1758,7 @@
         <v>53</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
         <v>54</v>
@@ -1774,7 +1781,7 @@
         <v>55</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
         <v>56</v>
@@ -1797,7 +1804,7 @@
         <v>57</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -1817,13 +1824,13 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D29">
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1840,10 +1847,10 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D30">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
         <v>61</v>
@@ -1866,7 +1873,7 @@
         <v>62</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E31" t="s">
         <v>63</v>
@@ -1878,6 +1885,29 @@
         <v>2</v>
       </c>
       <c r="H31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="B32">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
   <si>
     <t>#</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>LevelCompleteUIForm</t>
+  </si>
+  <si>
+    <t>补充生命值界面</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1221,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1908,6 +1914,29 @@
         <v>2</v>
       </c>
       <c r="H32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+      <c r="H33" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>AddLifeUIForm</t>
+  </si>
+  <si>
+    <t>补充球界面</t>
+  </si>
+  <si>
+    <t>AddBallsUIForm</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1937,6 +1943,29 @@
         <v>2</v>
       </c>
       <c r="H33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -264,6 +264,18 @@
   <si>
     <t>AddBallsUIForm</t>
   </si>
+  <si>
+    <t>补充道具界面</t>
+  </si>
+  <si>
+    <t>AddPropUIForm</t>
+  </si>
+  <si>
+    <t>关卡准备界面</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm</t>
+  </si>
 </sst>
 </file>
 
@@ -275,7 +287,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,7 +300,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -296,14 +308,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -319,7 +331,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -350,7 +362,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -358,7 +370,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -366,7 +378,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,14 +386,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -389,42 +401,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -485,19 +490,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,19 +514,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,19 +538,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,19 +562,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,19 +586,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,19 +610,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,7 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -806,10 +811,10 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -818,10 +823,10 @@
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -830,10 +835,10 @@
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -842,10 +847,10 @@
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -854,10 +859,10 @@
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -866,10 +871,10 @@
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -931,7 +936,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1106,7 +1325,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -1115,13 +1334,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1155,17 +1374,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1227,7 +1435,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1969,9 +2177,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35" spans="2:8">
+      <c r="B35">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>PrelevelUIForm</t>
+  </si>
+  <si>
+    <t>加载界面</t>
+  </si>
+  <si>
+    <t>LoadingUIForm</t>
   </si>
 </sst>
 </file>
@@ -1435,7 +1441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -2220,6 +2226,29 @@
         <v>2</v>
       </c>
       <c r="H36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -1,447 +1,172 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\Core\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>UI界面表</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>SortOrder</t>
-  </si>
-  <si>
-    <t>UIPrefab</t>
-  </si>
-  <si>
-    <t>PauseCoveredUI</t>
-  </si>
-  <si>
-    <t>UIGroupId</t>
-  </si>
-  <si>
-    <t>EscapeClose</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nt</t>
-    </r>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>显示顺序,相对于Group,每个Group间隔100</t>
-  </si>
-  <si>
-    <t>同组界面被覆盖时是否隐藏</t>
-  </si>
-  <si>
-    <t>UI组Id</t>
-  </si>
-  <si>
-    <t>返回键触发关闭界面</t>
-  </si>
-  <si>
-    <t>主界面(顶层)</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm</t>
-  </si>
-  <si>
-    <t>ArrowMazeWinUIForm</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm</t>
-  </si>
-  <si>
-    <t>顶部资源栏</t>
-  </si>
-  <si>
-    <t>ArrowUITopbar</t>
-  </si>
-  <si>
-    <t>大厅tab</t>
-  </si>
-  <si>
-    <t>HallTabUIForm</t>
-  </si>
-  <si>
-    <t>大厅主界面</t>
-  </si>
-  <si>
-    <t>HomePageUIForm</t>
-  </si>
-  <si>
-    <t>设置界面</t>
-  </si>
-  <si>
-    <t>SettingPageUIForm</t>
-  </si>
-  <si>
-    <t>任务界面</t>
-  </si>
-  <si>
-    <t>TaskPageUIForm</t>
-  </si>
-  <si>
-    <t>退出确认界面</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm</t>
-  </si>
-  <si>
-    <t>对话框(中层)</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog</t>
-  </si>
-  <si>
-    <t>语言设置</t>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
-  </si>
-  <si>
-    <t>提示(顶层)</t>
-  </si>
-  <si>
-    <t>吐司提示</t>
-  </si>
-  <si>
-    <t>ArrowToastTips</t>
-  </si>
-  <si>
-    <t>奖励弹窗</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm</t>
-  </si>
-  <si>
-    <t>PrivacyPolicy隐私协议</t>
-  </si>
-  <si>
-    <t>ArrowPrivacyPolicyUIForm</t>
-  </si>
-  <si>
-    <t>GuideUIForm</t>
-  </si>
-  <si>
-    <t>ArrowGuideUIForm</t>
-  </si>
-  <si>
-    <t>奖励领取界面</t>
-  </si>
-  <si>
-    <t>ArrowRewardUIForm</t>
-  </si>
-  <si>
-    <t>提现界面</t>
-  </si>
-  <si>
-    <t>MakeupUIForm</t>
-  </si>
-  <si>
-    <t>提现方式界面</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm</t>
-  </si>
-  <si>
-    <t>提现信息界面</t>
-  </si>
-  <si>
-    <t>MakeupInfoUIForm</t>
-  </si>
-  <si>
-    <t>提现记录界面</t>
-  </si>
-  <si>
-    <t>MakeupRecordUIForm</t>
-  </si>
-  <si>
-    <t>玩法界面</t>
-  </si>
-  <si>
-    <t>PlayUIForm</t>
-  </si>
-  <si>
-    <t>p卡领取界面</t>
-  </si>
-  <si>
-    <t>PcardRewardUIForm</t>
-  </si>
-  <si>
-    <t>PcardGiftUIForm</t>
-  </si>
-  <si>
-    <t>测试界面</t>
-  </si>
-  <si>
-    <t>DebugUIForm</t>
-  </si>
-  <si>
-    <t>通关界面</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm</t>
-  </si>
-  <si>
-    <t>补充生命值界面</t>
-  </si>
-  <si>
-    <t>AddLifeUIForm</t>
-  </si>
-  <si>
-    <t>补充球界面</t>
-  </si>
-  <si>
-    <t>AddBallsUIForm</t>
-  </si>
-  <si>
-    <t>补充道具界面</t>
-  </si>
-  <si>
-    <t>AddPropUIForm</t>
-  </si>
-  <si>
-    <t>关卡准备界面</t>
-  </si>
-  <si>
-    <t>PrelevelUIForm</t>
-  </si>
-  <si>
-    <t>加载界面</t>
-  </si>
-  <si>
-    <t>LoadingUIForm</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="19">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -742,154 +467,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1135,7 +860,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1144,7 +869,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1157,11 +882,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1439,843 +1227,1041 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="40.125" customWidth="1"/>
-    <col min="5" max="5" width="24.5" customWidth="1"/>
-    <col min="6" max="6" width="25.5" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="19.25" customWidth="1"/>
+    <col width="13.125" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15.125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="40.125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="24.5" customWidth="1" style="1" min="5" max="5"/>
+    <col width="25.5" customWidth="1" style="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" style="1" min="7" max="7"/>
+    <col width="19.25" customWidth="1" style="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UI界面表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UIPrefab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PauseCoveredUI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UIGroupId</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EscapeClose</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>显示顺序,相对于Group,每个Group间隔100</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>同组界面被覆盖时是否隐藏</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>UI组Id</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>返回键触发关闭界面</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>主界面(顶层)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ArrowMazeUIForm</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ArrowMazeUIForm</t>
+        </is>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
+    <row r="7">
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ArrowMazeWinUIForm</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ArrowMazeWinUIForm</t>
+        </is>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="B8">
+    <row r="8">
+      <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ArrowMazeOverUIForm</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ArrowMazeOverUIForm</t>
+        </is>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="B9">
+    <row r="9">
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>22</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>顶部资源栏</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ArrowUITopbar</t>
+        </is>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1"/>
-      <c r="B10">
+    <row r="10">
+      <c r="B10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>大厅tab</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HallTabUIForm</t>
+        </is>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1"/>
-      <c r="B11">
+    <row r="11">
+      <c r="B11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>大厅主界面</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="s">
-        <v>26</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HomePageUIForm</t>
+        </is>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1"/>
-      <c r="B12">
+    <row r="12">
+      <c r="B12" t="n">
         <v>7</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>设置界面</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
-        <v>28</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SettingPageUIForm</t>
+        </is>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1"/>
-      <c r="B13">
+    <row r="13">
+      <c r="B13" t="n">
         <v>8</v>
       </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>任务界面</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
-        <v>30</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TaskPageUIForm</t>
+        </is>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1"/>
-      <c r="B14">
+    <row r="14">
+      <c r="B14" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>退出确认界面</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>QuitConfirmUIForm</t>
+        </is>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>对话框(中层)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>35</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ArrowSettingDialog</t>
+        </is>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="B17">
+    <row r="17">
+      <c r="B17" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>37</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>语言设置</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LanguagesDialog</t>
+        </is>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="B19">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>提示(顶层)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>吐司提示</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="s">
-        <v>40</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ArrowToastTips</t>
+        </is>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="B20">
+    <row r="20">
+      <c r="B20" t="n">
         <v>13</v>
       </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>奖励弹窗</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="s">
-        <v>42</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ArrowRewardDialogUIForm</t>
+        </is>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="B21">
+    <row r="21">
+      <c r="B21" t="n">
         <v>14</v>
       </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PrivacyPolicy隐私协议</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
-        <v>44</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ArrowPrivacyPolicyUIForm</t>
+        </is>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="B22">
+    <row r="22">
+      <c r="B22" t="n">
         <v>15</v>
       </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GuideUIForm</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ArrowGuideUIForm</t>
+        </is>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="B23">
+    <row r="23">
+      <c r="B23" t="n">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>奖励领取界面</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>13</v>
       </c>
-      <c r="E23" t="s">
-        <v>48</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ArrowRewardUIForm</t>
+        </is>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="B24">
+    <row r="24">
+      <c r="B24" t="n">
         <v>17</v>
       </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>提现界面</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>15</v>
       </c>
-      <c r="E24" t="s">
-        <v>50</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MakeupUIForm</t>
+        </is>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="B25">
+    <row r="25">
+      <c r="B25" t="n">
         <v>18</v>
       </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>提现方式界面</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>16</v>
       </c>
-      <c r="E25" t="s">
-        <v>52</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MakeupPaymentUIForm</t>
+        </is>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="B26">
+    <row r="26">
+      <c r="B26" t="n">
         <v>19</v>
       </c>
-      <c r="C26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>提现信息界面</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="s">
-        <v>54</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MakeupInfoUIForm</t>
+        </is>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="B27">
+    <row r="27">
+      <c r="B27" t="n">
         <v>20</v>
       </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>提现记录界面</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>17</v>
       </c>
-      <c r="E27" t="s">
-        <v>56</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MakeupRecordUIForm</t>
+        </is>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="B28">
+    <row r="28">
+      <c r="B28" t="n">
         <v>21</v>
       </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>玩法界面</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>12</v>
       </c>
-      <c r="E28" t="s">
-        <v>58</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PlayUIForm</t>
+        </is>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="B29">
+    <row r="29">
+      <c r="B29" t="n">
         <v>22</v>
       </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>p卡领取界面</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>13</v>
       </c>
-      <c r="E29" t="s">
-        <v>60</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PcardRewardUIForm</t>
+        </is>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="B30">
+    <row r="30">
+      <c r="B30" t="n">
         <v>23</v>
       </c>
-      <c r="C30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>p卡领取界面</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>13</v>
       </c>
-      <c r="E30" t="s">
-        <v>61</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PcardGiftUIForm</t>
+        </is>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="B31">
+    <row r="31">
+      <c r="B31" t="n">
         <v>24</v>
       </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>测试界面</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>30</v>
       </c>
-      <c r="E31" t="s">
-        <v>63</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DebugUIForm</t>
+        </is>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="B32">
+    <row r="32">
+      <c r="B32" t="n">
         <v>25</v>
       </c>
-      <c r="C32" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>通关界面</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>13</v>
       </c>
-      <c r="E32" t="s">
-        <v>65</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LevelCompleteUIForm</t>
+        </is>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33">
+    <row r="33">
+      <c r="B33" t="n">
         <v>26</v>
       </c>
-      <c r="C33" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>补充生命值界面</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>13</v>
       </c>
-      <c r="E33" t="s">
-        <v>67</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AddLifeUIForm</t>
+        </is>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34">
+    <row r="34">
+      <c r="B34" t="n">
         <v>27</v>
       </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>补充球界面</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>13</v>
       </c>
-      <c r="E34" t="s">
-        <v>69</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AddBallsUIForm</t>
+        </is>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35">
+    <row r="35">
+      <c r="B35" t="n">
         <v>28</v>
       </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>补充道具界面</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>14</v>
       </c>
-      <c r="E35" t="s">
-        <v>71</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AddPropUIForm</t>
+        </is>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>2</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36">
+    <row r="36">
+      <c r="B36" t="n">
         <v>29</v>
       </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>关卡准备界面</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>13</v>
       </c>
-      <c r="E36" t="s">
-        <v>73</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PrelevelUIForm</t>
+        </is>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37">
+    <row r="37">
+      <c r="B37" t="n">
         <v>30</v>
       </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>加载界面</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>20</v>
       </c>
-      <c r="E37" t="s">
-        <v>75</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LoadingUIForm</t>
+        </is>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>31</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Coin and Life bar</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ArrowUITopbarSub</t>
+        </is>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -1,172 +1,437 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\Core\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17775" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>UI界面表</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SortOrder</t>
+  </si>
+  <si>
+    <t>UIPrefab</t>
+  </si>
+  <si>
+    <t>PauseCoveredUI</t>
+  </si>
+  <si>
+    <t>UIGroupId</t>
+  </si>
+  <si>
+    <t>EscapeClose</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>显示顺序,相对于Group,每个Group间隔100</t>
+  </si>
+  <si>
+    <t>同组界面被覆盖时是否隐藏</t>
+  </si>
+  <si>
+    <t>UI组Id</t>
+  </si>
+  <si>
+    <t>返回键触发关闭界面</t>
+  </si>
+  <si>
+    <t>主界面(顶层)</t>
+  </si>
+  <si>
+    <t>ArrowMazeUIForm</t>
+  </si>
+  <si>
+    <t>ArrowMazeWinUIForm</t>
+  </si>
+  <si>
+    <t>ArrowMazeOverUIForm</t>
+  </si>
+  <si>
+    <t>顶部资源栏</t>
+  </si>
+  <si>
+    <t>ArrowUITopbar</t>
+  </si>
+  <si>
+    <t>大厅tab</t>
+  </si>
+  <si>
+    <t>HallTabUIForm</t>
+  </si>
+  <si>
+    <t>大厅主界面</t>
+  </si>
+  <si>
+    <t>HomePageUIForm</t>
+  </si>
+  <si>
+    <t>设置界面</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm</t>
+  </si>
+  <si>
+    <t>任务界面</t>
+  </si>
+  <si>
+    <t>TaskPageUIForm</t>
+  </si>
+  <si>
+    <t>退出确认界面</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm</t>
+  </si>
+  <si>
+    <t>对话框(中层)</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>ArrowSettingDialog</t>
+  </si>
+  <si>
+    <t>语言设置</t>
+  </si>
+  <si>
+    <t>LanguagesDialog</t>
+  </si>
+  <si>
+    <t>提示(顶层)</t>
+  </si>
+  <si>
+    <t>吐司提示</t>
+  </si>
+  <si>
+    <t>ArrowToastTips</t>
+  </si>
+  <si>
+    <t>奖励弹窗</t>
+  </si>
+  <si>
+    <t>ArrowRewardDialogUIForm</t>
+  </si>
+  <si>
+    <t>PrivacyPolicy隐私协议</t>
+  </si>
+  <si>
+    <t>ArrowPrivacyPolicyUIForm</t>
+  </si>
+  <si>
+    <t>GuideUIForm</t>
+  </si>
+  <si>
+    <t>ArrowGuideUIForm</t>
+  </si>
+  <si>
+    <t>奖励领取界面</t>
+  </si>
+  <si>
+    <t>ArrowRewardUIForm</t>
+  </si>
+  <si>
+    <t>提现界面</t>
+  </si>
+  <si>
+    <t>MakeupUIForm</t>
+  </si>
+  <si>
+    <t>提现方式界面</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm</t>
+  </si>
+  <si>
+    <t>提现信息界面</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm</t>
+  </si>
+  <si>
+    <t>提现记录界面</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm</t>
+  </si>
+  <si>
+    <t>玩法界面</t>
+  </si>
+  <si>
+    <t>PlayUIForm</t>
+  </si>
+  <si>
+    <t>p卡领取界面</t>
+  </si>
+  <si>
+    <t>PcardRewardUIForm</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm</t>
+  </si>
+  <si>
+    <t>测试界面</t>
+  </si>
+  <si>
+    <t>DebugUIForm</t>
+  </si>
+  <si>
+    <t>通关界面</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm</t>
+  </si>
+  <si>
+    <t>补充生命值界面</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm</t>
+  </si>
+  <si>
+    <t>补充球界面</t>
+  </si>
+  <si>
+    <t>AddBallsUIForm</t>
+  </si>
+  <si>
+    <t>补充道具界面</t>
+  </si>
+  <si>
+    <t>AddPropUIForm</t>
+  </si>
+  <si>
+    <t>关卡准备界面</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm</t>
+  </si>
+  <si>
+    <t>加载界面</t>
+  </si>
+  <si>
+    <t>LoadingUIForm</t>
+  </si>
+  <si>
+    <t>Coin and Life bar</t>
+  </si>
+  <si>
+    <t>ArrowUITopbarSub</t>
+  </si>
+  <si>
+    <t>金币奖励界面</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -467,154 +732,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -860,7 +1124,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -869,7 +1133,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -882,74 +1146,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1227,1041 +1428,878 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H38"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col width="13.125" customWidth="1" style="1" min="2" max="2"/>
-    <col width="15.125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="40.125" customWidth="1" style="1" min="4" max="4"/>
-    <col width="24.5" customWidth="1" style="1" min="5" max="5"/>
-    <col width="25.5" customWidth="1" style="1" min="6" max="6"/>
-    <col width="10.5" customWidth="1" style="1" min="7" max="7"/>
-    <col width="19.25" customWidth="1" style="1" min="8" max="8"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="40.125" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>UI界面表</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SortOrder</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>UIPrefab</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PauseCoveredUI</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>UIGroupId</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EscapeClose</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>显示顺序,相对于Group,每个Group间隔100</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>同组界面被覆盖时是否隐藏</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>UI组Id</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>返回键触发关闭界面</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>主界面(顶层)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="n">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ArrowMazeUIForm</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ArrowMazeUIForm</t>
-        </is>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ArrowMazeWinUIForm</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:8">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ArrowMazeWinUIForm</t>
-        </is>
+      <c r="E7" t="s">
+        <v>18</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>2</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="n">
+    <row r="8" spans="1:8">
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ArrowMazeOverUIForm</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ArrowMazeOverUIForm</t>
-        </is>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="n">
+    <row r="9" spans="1:8">
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>顶部资源栏</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ArrowUITopbar</t>
-        </is>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="n">
+    <row r="10" spans="1:8">
+      <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>大厅tab</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HallTabUIForm</t>
-        </is>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="n">
+    <row r="11" spans="1:8">
+      <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>大厅主界面</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HomePageUIForm</t>
-        </is>
+      <c r="E11" t="s">
+        <v>25</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="n">
+    <row r="12" spans="1:8">
+      <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>设置界面</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SettingPageUIForm</t>
-        </is>
+      <c r="E12" t="s">
+        <v>27</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>1</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="n">
+    <row r="13" spans="1:8">
+      <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>任务界面</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TaskPageUIForm</t>
-        </is>
+      <c r="E13" t="s">
+        <v>29</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="n">
+    <row r="14" spans="1:8">
+      <c r="B14">
         <v>9</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>退出确认界面</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>QuitConfirmUIForm</t>
-        </is>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>对话框(中层)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16">
         <v>10</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16">
         <v>3</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ArrowSettingDialog</t>
-        </is>
+      <c r="E16" t="s">
+        <v>34</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="n">
+    <row r="17" spans="1:8">
+      <c r="B17">
         <v>11</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>语言设置</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LanguagesDialog</t>
-        </is>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>提示(顶层)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="n">
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="B19">
         <v>12</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>吐司提示</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ArrowToastTips</t>
-        </is>
+      <c r="E19" t="s">
+        <v>39</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>4</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="n">
+    <row r="20" spans="1:8">
+      <c r="B20">
         <v>13</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>奖励弹窗</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ArrowRewardDialogUIForm</t>
-        </is>
+      <c r="E20" t="s">
+        <v>41</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>2</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" t="n">
+    <row r="21" spans="1:8">
+      <c r="B21">
         <v>14</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PrivacyPolicy隐私协议</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21">
         <v>20</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ArrowPrivacyPolicyUIForm</t>
-        </is>
+      <c r="E21" t="s">
+        <v>43</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" t="n">
+    <row r="22" spans="1:8">
+      <c r="B22">
         <v>15</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GuideUIForm</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ArrowGuideUIForm</t>
-        </is>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>4</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="n">
+    <row r="23" spans="1:8">
+      <c r="B23">
         <v>16</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>奖励领取界面</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23">
         <v>13</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ArrowRewardUIForm</t>
-        </is>
+      <c r="E23" t="s">
+        <v>47</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>2</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="n">
+    <row r="24" spans="1:8">
+      <c r="B24">
         <v>17</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>提现界面</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24">
         <v>15</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MakeupUIForm</t>
-        </is>
+      <c r="E24" t="s">
+        <v>49</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="n">
+    <row r="25" spans="1:8">
+      <c r="B25">
         <v>18</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>提现方式界面</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
         <v>16</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MakeupPaymentUIForm</t>
-        </is>
+      <c r="E25" t="s">
+        <v>51</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>2</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="n">
+    <row r="26" spans="1:8">
+      <c r="B26">
         <v>19</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>提现信息界面</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26">
         <v>16</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MakeupInfoUIForm</t>
-        </is>
+      <c r="E26" t="s">
+        <v>53</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>2</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="n">
+    <row r="27" spans="1:8">
+      <c r="B27">
         <v>20</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>提现记录界面</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27">
         <v>17</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MakeupRecordUIForm</t>
-        </is>
+      <c r="E27" t="s">
+        <v>55</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>2</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" t="n">
+    <row r="28" spans="1:8">
+      <c r="B28">
         <v>21</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>玩法界面</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28">
         <v>12</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>PlayUIForm</t>
-        </is>
+      <c r="E28" t="s">
+        <v>57</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>2</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="n">
+    <row r="29" spans="1:8">
+      <c r="B29">
         <v>22</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>p卡领取界面</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29">
         <v>13</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>PcardRewardUIForm</t>
-        </is>
+      <c r="E29" t="s">
+        <v>59</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>2</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="n">
+    <row r="30" spans="1:8">
+      <c r="B30">
         <v>23</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>p卡领取界面</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
+      <c r="C30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30">
         <v>13</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PcardGiftUIForm</t>
-        </is>
+      <c r="E30" t="s">
+        <v>60</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>2</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" t="n">
+    <row r="31" spans="1:8">
+      <c r="B31">
         <v>24</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>测试界面</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31">
         <v>30</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>DebugUIForm</t>
-        </is>
+      <c r="E31" t="s">
+        <v>62</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>2</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="n">
+    <row r="32" spans="1:8">
+      <c r="B32">
         <v>25</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>通关界面</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32">
         <v>13</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LevelCompleteUIForm</t>
-        </is>
+      <c r="E32" t="s">
+        <v>64</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>2</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" t="n">
+    <row r="33" spans="2:8">
+      <c r="B33">
         <v>26</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>补充生命值界面</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
+      <c r="C33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33">
         <v>13</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AddLifeUIForm</t>
-        </is>
+      <c r="E33" t="s">
+        <v>66</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>2</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="n">
+    <row r="34" spans="2:8">
+      <c r="B34">
         <v>27</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>补充球界面</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
+      <c r="C34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34">
         <v>13</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AddBallsUIForm</t>
-        </is>
+      <c r="E34" t="s">
+        <v>68</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>2</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" t="n">
+    <row r="35" spans="2:8">
+      <c r="B35">
         <v>28</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>补充道具界面</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35">
         <v>14</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AddPropUIForm</t>
-        </is>
+      <c r="E35" t="s">
+        <v>70</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>2</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="n">
+    <row r="36" spans="2:8">
+      <c r="B36">
         <v>29</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>关卡准备界面</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36">
         <v>13</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PrelevelUIForm</t>
-        </is>
+      <c r="E36" t="s">
+        <v>72</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>2</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" t="n">
+    <row r="37" spans="2:8">
+      <c r="B37">
         <v>30</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>加载界面</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37">
         <v>20</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>LoadingUIForm</t>
-        </is>
+      <c r="E37" t="s">
+        <v>74</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>2</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="n">
+    <row r="38" spans="2:8">
+      <c r="B38">
         <v>31</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Coin and Life bar</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38">
         <v>3</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ArrowUITopbarSub</t>
-        </is>
+      <c r="E38" t="s">
+        <v>76</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
   <si>
     <t>#</t>
   </si>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <t>CoinRewardUIForm</t>
+  </si>
+  <si>
+    <t>玩法Loading界面</t>
+  </si>
+  <si>
+    <t>PlayLoadingUIForm</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -2273,6 +2279,29 @@
         <v>2</v>
       </c>
       <c r="H39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>MakeupPaymentUIForm</t>
+  </si>
+  <si>
+    <t>提现方式成功界面</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm</t>
   </si>
   <si>
     <t>提现信息界面</t>
@@ -1436,7 +1442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1968,7 +1974,7 @@
         <v>52</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
         <v>53</v>
@@ -1991,7 +1997,7 @@
         <v>54</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
@@ -2014,7 +2020,7 @@
         <v>56</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
         <v>57</v>
@@ -2037,7 +2043,7 @@
         <v>58</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
         <v>59</v>
@@ -2057,13 +2063,13 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D30">
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -2080,10 +2086,10 @@
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
         <v>62</v>
@@ -2106,7 +2112,7 @@
         <v>63</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
         <v>64</v>
@@ -2175,7 +2181,7 @@
         <v>69</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
         <v>70</v>
@@ -2198,7 +2204,7 @@
         <v>71</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s">
         <v>72</v>
@@ -2221,7 +2227,7 @@
         <v>73</v>
       </c>
       <c r="D37">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
         <v>74</v>
@@ -2244,7 +2250,7 @@
         <v>75</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E38" t="s">
         <v>76</v>
@@ -2253,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
@@ -2267,7 +2273,7 @@
         <v>77</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
         <v>78</v>
@@ -2276,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
@@ -2290,7 +2296,7 @@
         <v>79</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
         <v>80</v>
@@ -2302,6 +2308,29 @@
         <v>2</v>
       </c>
       <c r="H40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>#</t>
   </si>
@@ -84,24 +84,18 @@
     <t>返回键触发关闭界面</t>
   </si>
   <si>
-    <t>主界面(顶层)</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm</t>
-  </si>
-  <si>
-    <t>ArrowMazeWinUIForm</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm</t>
-  </si>
-  <si>
     <t>顶部资源栏</t>
   </si>
   <si>
     <t>ArrowUITopbar</t>
   </si>
   <si>
+    <t>Coin and Life bar</t>
+  </si>
+  <si>
+    <t>ArrowUITopbarSub</t>
+  </si>
+  <si>
     <t>大厅tab</t>
   </si>
   <si>
@@ -132,36 +126,12 @@
     <t>QuitConfirmUIForm</t>
   </si>
   <si>
-    <t>对话框(中层)</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog</t>
-  </si>
-  <si>
-    <t>语言设置</t>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
-  </si>
-  <si>
-    <t>提示(顶层)</t>
-  </si>
-  <si>
     <t>吐司提示</t>
   </si>
   <si>
     <t>ArrowToastTips</t>
   </si>
   <si>
-    <t>奖励弹窗</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm</t>
-  </si>
-  <si>
     <t>PrivacyPolicy隐私协议</t>
   </si>
   <si>
@@ -174,12 +144,6 @@
     <t>ArrowGuideUIForm</t>
   </si>
   <si>
-    <t>奖励领取界面</t>
-  </si>
-  <si>
-    <t>ArrowRewardUIForm</t>
-  </si>
-  <si>
     <t>提现界面</t>
   </si>
   <si>
@@ -265,12 +229,6 @@
   </si>
   <si>
     <t>LoadingUIForm</t>
-  </si>
-  <si>
-    <t>Coin and Life bar</t>
-  </si>
-  <si>
-    <t>ArrowUITopbarSub</t>
   </si>
   <si>
     <t>金币奖励界面</t>
@@ -441,12 +399,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -765,7 +741,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -789,16 +765,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -807,90 +783,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1442,7 +1421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -1529,28 +1508,43 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1561,22 +1555,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -1584,22 +1578,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -1607,16 +1601,16 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
         <v>20</v>
       </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1630,16 +1624,16 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1653,16 +1647,16 @@
     </row>
     <row r="11" spans="1:8">
       <c r="B11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1676,16 +1670,16 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1699,16 +1693,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -1722,16 +1716,16 @@
     </row>
     <row r="14" spans="1:8">
       <c r="B14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -1744,593 +1738,393 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16">
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>3</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18">
         <v>2</v>
       </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="B17">
-        <v>11</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17">
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="E17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17">
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20">
         <v>2</v>
       </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="B19">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19">
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27">
         <v>4</v>
       </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="B20">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="B21">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21">
+      <c r="E27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="B22">
-        <v>15</v>
-      </c>
-      <c r="C22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>4</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="B23">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="B24">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="B25">
-        <v>18</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25">
-        <v>16</v>
-      </c>
-      <c r="E25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="B26">
-        <v>19</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26">
-        <v>17</v>
-      </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="B27">
-        <v>20</v>
-      </c>
-      <c r="C27" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="B28">
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>3</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30">
         <v>21</v>
       </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28">
-        <v>17</v>
-      </c>
-      <c r="E28" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>2</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="B29">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>2</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="B30">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30">
-        <v>13</v>
-      </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="2:8">
       <c r="B31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="B32">
-        <v>25</v>
-      </c>
-      <c r="C32" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32">
-        <v>30</v>
-      </c>
-      <c r="E32" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33">
-        <v>26</v>
-      </c>
-      <c r="C33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>2</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34">
-        <v>27</v>
-      </c>
-      <c r="C34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35">
-        <v>28</v>
-      </c>
-      <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>2</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36">
-        <v>29</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="B37">
-        <v>30</v>
-      </c>
-      <c r="C37" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="B38">
-        <v>31</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8">
-      <c r="B39">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39" t="s">
-        <v>78</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40">
-        <v>33</v>
-      </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s">
-        <v>80</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41">
-        <v>34</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>82</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-      <c r="H41" t="b">
         <v>0</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -1607,7 +1607,7 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
@@ -1630,7 +1630,7 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -1653,7 +1653,7 @@
         <v>28</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>53</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>54</v>
@@ -1975,7 +1975,7 @@
         <v>55</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>56</v>
@@ -1998,7 +1998,7 @@
         <v>57</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -2021,7 +2021,7 @@
         <v>59</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
         <v>60</v>
@@ -2044,7 +2044,7 @@
         <v>61</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="s">
         <v>62</v>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>

--- a/AAAGameData/DataTables/Core/ArrowUITable.xlsx
+++ b/AAAGameData/DataTables/Core/ArrowUITable.xlsx
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
